--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N97_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N97_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.683563491127982</v>
+        <v>1.573579067308297</v>
       </c>
       <c r="D2" t="n">
-        <v>16.00105344433813</v>
+        <v>2.600171184704946</v>
       </c>
       <c r="E2" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F2" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.72447627444166</v>
+        <v>8.08022739459677</v>
       </c>
       <c r="D3" t="n">
-        <v>53.19530858068423</v>
+        <v>8.644237644361189</v>
       </c>
       <c r="E3" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F3" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.59707590751306</v>
+        <v>6.272024834970872</v>
       </c>
       <c r="D4" t="n">
-        <v>38.12105870326489</v>
+        <v>6.194672039280546</v>
       </c>
       <c r="E4" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F4" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.78522745774414</v>
+        <v>2.890099461883423</v>
       </c>
       <c r="D5" t="n">
-        <v>14.60948048887671</v>
+        <v>2.374040579442465</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F5" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.05775259984872</v>
+        <v>2.121884797475418</v>
       </c>
       <c r="D6" t="n">
-        <v>13.27310092767125</v>
+        <v>2.156878900746579</v>
       </c>
       <c r="E6" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F6" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.31916899903572</v>
+        <v>3.139364962343305</v>
       </c>
       <c r="D7" t="n">
-        <v>19.82423962388258</v>
+        <v>3.221438938880919</v>
       </c>
       <c r="E7" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F7" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.2042648663165</v>
+        <v>5.720693040776432</v>
       </c>
       <c r="D8" t="n">
-        <v>15.38038272734154</v>
+        <v>2.499312193193</v>
       </c>
       <c r="E8" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F8" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.95156626812358</v>
+        <v>7.954629518570082</v>
       </c>
       <c r="D9" t="n">
-        <v>48.69767567667869</v>
+        <v>7.913372297460287</v>
       </c>
       <c r="E9" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F9" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.99456094184401</v>
+        <v>7.961616153049652</v>
       </c>
       <c r="D10" t="n">
-        <v>48.88173995266403</v>
+        <v>7.943282742307906</v>
       </c>
       <c r="E10" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F10" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.62214096940178</v>
+        <v>5.951097907527789</v>
       </c>
       <c r="D11" t="n">
-        <v>38.09177126183911</v>
+        <v>6.189912830048856</v>
       </c>
       <c r="E11" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F11" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.54880518537521</v>
+        <v>4.639180842623472</v>
       </c>
       <c r="D12" t="n">
-        <v>29.42105412812208</v>
+        <v>4.780921295819839</v>
       </c>
       <c r="E12" t="n">
-        <v>14.12388472148219</v>
+        <v>2.295131267240857</v>
       </c>
       <c r="F12" t="n">
-        <v>14.78042084691423</v>
+        <v>2.401818387623563</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
